--- a/(TESTING) automated_testing/automated_test_log.xlsx
+++ b/(TESTING) automated_testing/automated_test_log.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.109375" customWidth="1" min="1" max="1"/>
@@ -1837,6 +1837,129 @@
         <v>8</v>
       </c>
       <c r="K35" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-03-14 20:48:19</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>25</v>
+      </c>
+      <c r="H36" t="n">
+        <v>50</v>
+      </c>
+      <c r="I36" t="n">
+        <v>60</v>
+      </c>
+      <c r="J36" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-03-15 02:32:50</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.039128</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>25</v>
+      </c>
+      <c r="H37" t="n">
+        <v>50</v>
+      </c>
+      <c r="I37" t="n">
+        <v>60</v>
+      </c>
+      <c r="J37" t="n">
+        <v>8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-03-15 06:26:26</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.06572</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>25</v>
+      </c>
+      <c r="H38" t="n">
+        <v>50</v>
+      </c>
+      <c r="I38" t="n">
+        <v>60</v>
+      </c>
+      <c r="J38" t="n">
+        <v>8</v>
+      </c>
+      <c r="K38" t="n">
         <v>9</v>
       </c>
     </row>

--- a/(TESTING) automated_testing/automated_test_log.xlsx
+++ b/(TESTING) automated_testing/automated_test_log.xlsx
@@ -3,11 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="816" yWindow="3636" windowWidth="17280" windowHeight="9420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19090" yWindow="-6740" windowWidth="14620" windowHeight="25100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="backup" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model tracking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="backup" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$K$1</definedName>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -34,13 +35,27 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="22"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -64,6 +79,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.109375" customWidth="1" min="1" max="1"/>
@@ -1963,6 +1980,744 @@
         <v>9</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-03-31 16:47:00</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>100</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0848</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>25</v>
+      </c>
+      <c r="H39" t="n">
+        <v>50</v>
+      </c>
+      <c r="I39" t="n">
+        <v>60</v>
+      </c>
+      <c r="J39" t="n">
+        <v>8</v>
+      </c>
+      <c r="K39" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-03-31 17:01:03</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08396000000000001</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>25</v>
+      </c>
+      <c r="H40" t="n">
+        <v>50</v>
+      </c>
+      <c r="I40" t="n">
+        <v>60</v>
+      </c>
+      <c r="J40" t="n">
+        <v>8</v>
+      </c>
+      <c r="K40" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-03-31 17:28:38</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.03792</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>25</v>
+      </c>
+      <c r="H41" t="n">
+        <v>50</v>
+      </c>
+      <c r="I41" t="n">
+        <v>60</v>
+      </c>
+      <c r="J41" t="n">
+        <v>8</v>
+      </c>
+      <c r="K41" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-03-31 17:52:49</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.08368</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>6</v>
+      </c>
+      <c r="G42" t="n">
+        <v>25</v>
+      </c>
+      <c r="H42" t="n">
+        <v>50</v>
+      </c>
+      <c r="I42" t="n">
+        <v>60</v>
+      </c>
+      <c r="J42" t="n">
+        <v>8</v>
+      </c>
+      <c r="K42" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-03-31 22:45:19</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>100</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>25</v>
+      </c>
+      <c r="H43" t="n">
+        <v>50</v>
+      </c>
+      <c r="I43" t="n">
+        <v>60</v>
+      </c>
+      <c r="J43" t="n">
+        <v>8</v>
+      </c>
+      <c r="K43" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-04-02 18:44:21</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.08124000000000001</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" t="n">
+        <v>25</v>
+      </c>
+      <c r="H44" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" t="n">
+        <v>60</v>
+      </c>
+      <c r="J44" t="n">
+        <v>8</v>
+      </c>
+      <c r="K44" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-04-03 04:38:26</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.08172</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>6</v>
+      </c>
+      <c r="G45" t="n">
+        <v>25</v>
+      </c>
+      <c r="H45" t="n">
+        <v>50</v>
+      </c>
+      <c r="I45" t="n">
+        <v>60</v>
+      </c>
+      <c r="J45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K45" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-04-03 04:39:51</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.09616</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>25</v>
+      </c>
+      <c r="H46" t="n">
+        <v>50</v>
+      </c>
+      <c r="I46" t="n">
+        <v>60</v>
+      </c>
+      <c r="J46" t="n">
+        <v>8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-04-03 04:41:23</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.03368</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>6</v>
+      </c>
+      <c r="G47" t="n">
+        <v>25</v>
+      </c>
+      <c r="H47" t="n">
+        <v>50</v>
+      </c>
+      <c r="I47" t="n">
+        <v>60</v>
+      </c>
+      <c r="J47" t="n">
+        <v>8</v>
+      </c>
+      <c r="K47" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-04-03 04:42:50</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.06844</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>6</v>
+      </c>
+      <c r="G48" t="n">
+        <v>25</v>
+      </c>
+      <c r="H48" t="n">
+        <v>50</v>
+      </c>
+      <c r="I48" t="n">
+        <v>60</v>
+      </c>
+      <c r="J48" t="n">
+        <v>8</v>
+      </c>
+      <c r="K48" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-04-03 04:57:19</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.08416</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>6</v>
+      </c>
+      <c r="G49" t="n">
+        <v>25</v>
+      </c>
+      <c r="H49" t="n">
+        <v>50</v>
+      </c>
+      <c r="I49" t="n">
+        <v>60</v>
+      </c>
+      <c r="J49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K49" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-04-03 05:01:17</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.09498666666666666</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>6</v>
+      </c>
+      <c r="G50" t="n">
+        <v>25</v>
+      </c>
+      <c r="H50" t="n">
+        <v>50</v>
+      </c>
+      <c r="I50" t="n">
+        <v>60</v>
+      </c>
+      <c r="J50" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-04-03 05:05:35</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.03908</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>6</v>
+      </c>
+      <c r="G51" t="n">
+        <v>25</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" t="n">
+        <v>60</v>
+      </c>
+      <c r="J51" t="n">
+        <v>8</v>
+      </c>
+      <c r="K51" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-04-03 05:09:35</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.06785333333333333</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" t="n">
+        <v>25</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" t="n">
+        <v>60</v>
+      </c>
+      <c r="J52" t="n">
+        <v>8</v>
+      </c>
+      <c r="K52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-04-03 05:32:17</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.082704</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>25</v>
+      </c>
+      <c r="H53" t="n">
+        <v>50</v>
+      </c>
+      <c r="I53" t="n">
+        <v>60</v>
+      </c>
+      <c r="J53" t="n">
+        <v>8</v>
+      </c>
+      <c r="K53" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-04-03 05:38:44</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.096792</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54" t="n">
+        <v>25</v>
+      </c>
+      <c r="H54" t="n">
+        <v>50</v>
+      </c>
+      <c r="I54" t="n">
+        <v>60</v>
+      </c>
+      <c r="J54" t="n">
+        <v>8</v>
+      </c>
+      <c r="K54" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-04-03 05:45:46</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.038784</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>6</v>
+      </c>
+      <c r="G55" t="n">
+        <v>25</v>
+      </c>
+      <c r="H55" t="n">
+        <v>50</v>
+      </c>
+      <c r="I55" t="n">
+        <v>60</v>
+      </c>
+      <c r="J55" t="n">
+        <v>8</v>
+      </c>
+      <c r="K55" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-04-03 05:52:20</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.06765599999999999</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G56" t="n">
+        <v>25</v>
+      </c>
+      <c r="H56" t="n">
+        <v>50</v>
+      </c>
+      <c r="I56" t="n">
+        <v>60</v>
+      </c>
+      <c r="J56" t="n">
+        <v>8</v>
+      </c>
+      <c r="K56" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1">
     <sortState ref="A2:K27">
@@ -1974,6 +2729,77 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="54.109375" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="28.8" customHeight="1">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tuning changes made </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A2C_v2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added reward function for scheduling without delay </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>A2C_v3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Agent still take illegal actions, but able to complete the episode</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Increased reward for manage to schedule to  +5 and applied tanh squashing for the reward from self.allowance with a hardcoded scaling factor of 1000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/(TESTING) automated_testing/automated_test_log.xlsx
+++ b/(TESTING) automated_testing/automated_test_log.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19090" yWindow="-6740" windowWidth="14620" windowHeight="25100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.109375" customWidth="1" min="1" max="1"/>
@@ -2715,6 +2715,7386 @@
         <v>8</v>
       </c>
       <c r="K56" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-04-04 17:55:15</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>6</v>
+      </c>
+      <c r="G57" t="n">
+        <v>25</v>
+      </c>
+      <c r="H57" t="n">
+        <v>50</v>
+      </c>
+      <c r="I57" t="n">
+        <v>60</v>
+      </c>
+      <c r="J57" t="n">
+        <v>8</v>
+      </c>
+      <c r="K57" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-04-04 18:08:15</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>6</v>
+      </c>
+      <c r="G58" t="n">
+        <v>25</v>
+      </c>
+      <c r="H58" t="n">
+        <v>50</v>
+      </c>
+      <c r="I58" t="n">
+        <v>60</v>
+      </c>
+      <c r="J58" t="n">
+        <v>8</v>
+      </c>
+      <c r="K58" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-04-04 18:18:22</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>6</v>
+      </c>
+      <c r="G59" t="n">
+        <v>25</v>
+      </c>
+      <c r="H59" t="n">
+        <v>50</v>
+      </c>
+      <c r="I59" t="n">
+        <v>60</v>
+      </c>
+      <c r="J59" t="n">
+        <v>8</v>
+      </c>
+      <c r="K59" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-04-04 18:26:15</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>6</v>
+      </c>
+      <c r="G60" t="n">
+        <v>75</v>
+      </c>
+      <c r="H60" t="n">
+        <v>50</v>
+      </c>
+      <c r="I60" t="n">
+        <v>60</v>
+      </c>
+      <c r="J60" t="n">
+        <v>8</v>
+      </c>
+      <c r="K60" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-04-05 00:56:09</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>6</v>
+      </c>
+      <c r="G61" t="n">
+        <v>25</v>
+      </c>
+      <c r="H61" t="n">
+        <v>50</v>
+      </c>
+      <c r="I61" t="n">
+        <v>60</v>
+      </c>
+      <c r="J61" t="n">
+        <v>8</v>
+      </c>
+      <c r="K61" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-04-05 16:10:58</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>25</v>
+      </c>
+      <c r="H62" t="n">
+        <v>50</v>
+      </c>
+      <c r="I62" t="n">
+        <v>60</v>
+      </c>
+      <c r="J62" t="n">
+        <v>8</v>
+      </c>
+      <c r="K62" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-04-05 23:37:28</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>6</v>
+      </c>
+      <c r="G63" t="n">
+        <v>25</v>
+      </c>
+      <c r="H63" t="n">
+        <v>50</v>
+      </c>
+      <c r="I63" t="n">
+        <v>60</v>
+      </c>
+      <c r="J63" t="n">
+        <v>8</v>
+      </c>
+      <c r="K63" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:00:45</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>6</v>
+      </c>
+      <c r="G64" t="n">
+        <v>25</v>
+      </c>
+      <c r="H64" t="n">
+        <v>50</v>
+      </c>
+      <c r="I64" t="n">
+        <v>60</v>
+      </c>
+      <c r="J64" t="n">
+        <v>8</v>
+      </c>
+      <c r="K64" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:20:29</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>6</v>
+      </c>
+      <c r="G65" t="n">
+        <v>25</v>
+      </c>
+      <c r="H65" t="n">
+        <v>50</v>
+      </c>
+      <c r="I65" t="n">
+        <v>60</v>
+      </c>
+      <c r="J65" t="n">
+        <v>8</v>
+      </c>
+      <c r="K65" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:21:03</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>6</v>
+      </c>
+      <c r="G66" t="n">
+        <v>25</v>
+      </c>
+      <c r="H66" t="n">
+        <v>50</v>
+      </c>
+      <c r="I66" t="n">
+        <v>60</v>
+      </c>
+      <c r="J66" t="n">
+        <v>8</v>
+      </c>
+      <c r="K66" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:37:37</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>6</v>
+      </c>
+      <c r="G67" t="n">
+        <v>25</v>
+      </c>
+      <c r="H67" t="n">
+        <v>50</v>
+      </c>
+      <c r="I67" t="n">
+        <v>60</v>
+      </c>
+      <c r="J67" t="n">
+        <v>8</v>
+      </c>
+      <c r="K67" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:39:03</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>6</v>
+      </c>
+      <c r="G68" t="n">
+        <v>25</v>
+      </c>
+      <c r="H68" t="n">
+        <v>50</v>
+      </c>
+      <c r="I68" t="n">
+        <v>60</v>
+      </c>
+      <c r="J68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K68" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:39:51</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>6</v>
+      </c>
+      <c r="G69" t="n">
+        <v>26</v>
+      </c>
+      <c r="H69" t="n">
+        <v>50</v>
+      </c>
+      <c r="I69" t="n">
+        <v>60</v>
+      </c>
+      <c r="J69" t="n">
+        <v>8</v>
+      </c>
+      <c r="K69" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:40:49</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>6</v>
+      </c>
+      <c r="G70" t="n">
+        <v>25</v>
+      </c>
+      <c r="H70" t="n">
+        <v>50</v>
+      </c>
+      <c r="I70" t="n">
+        <v>60</v>
+      </c>
+      <c r="J70" t="n">
+        <v>8</v>
+      </c>
+      <c r="K70" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:49:12</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" t="n">
+        <v>50</v>
+      </c>
+      <c r="I71" t="n">
+        <v>60</v>
+      </c>
+      <c r="J71" t="n">
+        <v>8</v>
+      </c>
+      <c r="K71" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:52:44</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>6</v>
+      </c>
+      <c r="G72" t="n">
+        <v>30</v>
+      </c>
+      <c r="H72" t="n">
+        <v>50</v>
+      </c>
+      <c r="I72" t="n">
+        <v>60</v>
+      </c>
+      <c r="J72" t="n">
+        <v>8</v>
+      </c>
+      <c r="K72" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:53:10</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>6</v>
+      </c>
+      <c r="G73" t="n">
+        <v>25</v>
+      </c>
+      <c r="H73" t="n">
+        <v>50</v>
+      </c>
+      <c r="I73" t="n">
+        <v>60</v>
+      </c>
+      <c r="J73" t="n">
+        <v>8</v>
+      </c>
+      <c r="K73" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-04-06 00:54:23</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" t="n">
+        <v>28</v>
+      </c>
+      <c r="H74" t="n">
+        <v>50</v>
+      </c>
+      <c r="I74" t="n">
+        <v>60</v>
+      </c>
+      <c r="J74" t="n">
+        <v>8</v>
+      </c>
+      <c r="K74" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-04-06 01:00:23</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>6</v>
+      </c>
+      <c r="G75" t="n">
+        <v>30</v>
+      </c>
+      <c r="H75" t="n">
+        <v>50</v>
+      </c>
+      <c r="I75" t="n">
+        <v>60</v>
+      </c>
+      <c r="J75" t="n">
+        <v>8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-04-06 01:01:00</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>6</v>
+      </c>
+      <c r="G76" t="n">
+        <v>30</v>
+      </c>
+      <c r="H76" t="n">
+        <v>50</v>
+      </c>
+      <c r="I76" t="n">
+        <v>60</v>
+      </c>
+      <c r="J76" t="n">
+        <v>8</v>
+      </c>
+      <c r="K76" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-04-06 01:01:23</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" t="n">
+        <v>30</v>
+      </c>
+      <c r="H77" t="n">
+        <v>50</v>
+      </c>
+      <c r="I77" t="n">
+        <v>60</v>
+      </c>
+      <c r="J77" t="n">
+        <v>8</v>
+      </c>
+      <c r="K77" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-04-06 01:12:13</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>6</v>
+      </c>
+      <c r="G78" t="n">
+        <v>33</v>
+      </c>
+      <c r="H78" t="n">
+        <v>50</v>
+      </c>
+      <c r="I78" t="n">
+        <v>60</v>
+      </c>
+      <c r="J78" t="n">
+        <v>8</v>
+      </c>
+      <c r="K78" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-04-06 01:13:17</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>6</v>
+      </c>
+      <c r="G79" t="n">
+        <v>33</v>
+      </c>
+      <c r="H79" t="n">
+        <v>50</v>
+      </c>
+      <c r="I79" t="n">
+        <v>60</v>
+      </c>
+      <c r="J79" t="n">
+        <v>8</v>
+      </c>
+      <c r="K79" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-04-06 01:13:46</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>6</v>
+      </c>
+      <c r="G80" t="n">
+        <v>25</v>
+      </c>
+      <c r="H80" t="n">
+        <v>50</v>
+      </c>
+      <c r="I80" t="n">
+        <v>60</v>
+      </c>
+      <c r="J80" t="n">
+        <v>8</v>
+      </c>
+      <c r="K80" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-04-06 01:26:41</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>6</v>
+      </c>
+      <c r="G81" t="n">
+        <v>35</v>
+      </c>
+      <c r="H81" t="n">
+        <v>50</v>
+      </c>
+      <c r="I81" t="n">
+        <v>60</v>
+      </c>
+      <c r="J81" t="n">
+        <v>8</v>
+      </c>
+      <c r="K81" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-04-06 01:35:17</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>6</v>
+      </c>
+      <c r="G82" t="n">
+        <v>33</v>
+      </c>
+      <c r="H82" t="n">
+        <v>50</v>
+      </c>
+      <c r="I82" t="n">
+        <v>60</v>
+      </c>
+      <c r="J82" t="n">
+        <v>8</v>
+      </c>
+      <c r="K82" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-04-06 01:37:02</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>6</v>
+      </c>
+      <c r="G83" t="n">
+        <v>33</v>
+      </c>
+      <c r="H83" t="n">
+        <v>50</v>
+      </c>
+      <c r="I83" t="n">
+        <v>60</v>
+      </c>
+      <c r="J83" t="n">
+        <v>8</v>
+      </c>
+      <c r="K83" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-04-06 02:00:28</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>6</v>
+      </c>
+      <c r="G84" t="n">
+        <v>40</v>
+      </c>
+      <c r="H84" t="n">
+        <v>50</v>
+      </c>
+      <c r="I84" t="n">
+        <v>60</v>
+      </c>
+      <c r="J84" t="n">
+        <v>8</v>
+      </c>
+      <c r="K84" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-04-06 02:21:10</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>6</v>
+      </c>
+      <c r="G85" t="n">
+        <v>40</v>
+      </c>
+      <c r="H85" t="n">
+        <v>50</v>
+      </c>
+      <c r="I85" t="n">
+        <v>60</v>
+      </c>
+      <c r="J85" t="n">
+        <v>8</v>
+      </c>
+      <c r="K85" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-04-06 03:05:05</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>6</v>
+      </c>
+      <c r="G86" t="n">
+        <v>33</v>
+      </c>
+      <c r="H86" t="n">
+        <v>50</v>
+      </c>
+      <c r="I86" t="n">
+        <v>60</v>
+      </c>
+      <c r="J86" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:21:25</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>6</v>
+      </c>
+      <c r="G87" t="n">
+        <v>35</v>
+      </c>
+      <c r="H87" t="n">
+        <v>50</v>
+      </c>
+      <c r="I87" t="n">
+        <v>60</v>
+      </c>
+      <c r="J87" t="n">
+        <v>8</v>
+      </c>
+      <c r="K87" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:39:21</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.5428571428571428</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>6</v>
+      </c>
+      <c r="G88" t="n">
+        <v>35</v>
+      </c>
+      <c r="H88" t="n">
+        <v>50</v>
+      </c>
+      <c r="I88" t="n">
+        <v>60</v>
+      </c>
+      <c r="J88" t="n">
+        <v>8</v>
+      </c>
+      <c r="K88" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:39:54</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>6</v>
+      </c>
+      <c r="G89" t="n">
+        <v>25</v>
+      </c>
+      <c r="H89" t="n">
+        <v>50</v>
+      </c>
+      <c r="I89" t="n">
+        <v>60</v>
+      </c>
+      <c r="J89" t="n">
+        <v>8</v>
+      </c>
+      <c r="K89" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:40:30</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>6</v>
+      </c>
+      <c r="G90" t="n">
+        <v>26</v>
+      </c>
+      <c r="H90" t="n">
+        <v>50</v>
+      </c>
+      <c r="I90" t="n">
+        <v>60</v>
+      </c>
+      <c r="J90" t="n">
+        <v>8</v>
+      </c>
+      <c r="K90" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:41:52</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.4533333333333333</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>6</v>
+      </c>
+      <c r="G91" t="n">
+        <v>30</v>
+      </c>
+      <c r="H91" t="n">
+        <v>50</v>
+      </c>
+      <c r="I91" t="n">
+        <v>60</v>
+      </c>
+      <c r="J91" t="n">
+        <v>8</v>
+      </c>
+      <c r="K91" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:42:20</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>10</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.3866666666666667</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>6</v>
+      </c>
+      <c r="G92" t="n">
+        <v>30</v>
+      </c>
+      <c r="H92" t="n">
+        <v>50</v>
+      </c>
+      <c r="I92" t="n">
+        <v>60</v>
+      </c>
+      <c r="J92" t="n">
+        <v>8</v>
+      </c>
+      <c r="K92" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:43:40</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>10</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.4033333333333333</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>6</v>
+      </c>
+      <c r="G93" t="n">
+        <v>30</v>
+      </c>
+      <c r="H93" t="n">
+        <v>50</v>
+      </c>
+      <c r="I93" t="n">
+        <v>60</v>
+      </c>
+      <c r="J93" t="n">
+        <v>8</v>
+      </c>
+      <c r="K93" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:45:11</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>100</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>6</v>
+      </c>
+      <c r="G94" t="n">
+        <v>30</v>
+      </c>
+      <c r="H94" t="n">
+        <v>50</v>
+      </c>
+      <c r="I94" t="n">
+        <v>60</v>
+      </c>
+      <c r="J94" t="n">
+        <v>8</v>
+      </c>
+      <c r="K94" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:46:38</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>100</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.4293333333333333</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>6</v>
+      </c>
+      <c r="G95" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" t="n">
+        <v>50</v>
+      </c>
+      <c r="I95" t="n">
+        <v>60</v>
+      </c>
+      <c r="J95" t="n">
+        <v>8</v>
+      </c>
+      <c r="K95" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:48:06</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>100</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>6</v>
+      </c>
+      <c r="G96" t="n">
+        <v>30</v>
+      </c>
+      <c r="H96" t="n">
+        <v>50</v>
+      </c>
+      <c r="I96" t="n">
+        <v>60</v>
+      </c>
+      <c r="J96" t="n">
+        <v>8</v>
+      </c>
+      <c r="K96" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:50:14</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.5928571428571429</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>6</v>
+      </c>
+      <c r="G97" t="n">
+        <v>35</v>
+      </c>
+      <c r="H97" t="n">
+        <v>50</v>
+      </c>
+      <c r="I97" t="n">
+        <v>60</v>
+      </c>
+      <c r="J97" t="n">
+        <v>8</v>
+      </c>
+      <c r="K97" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:52:34</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>100</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.9054285714285715</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>6</v>
+      </c>
+      <c r="G98" t="n">
+        <v>35</v>
+      </c>
+      <c r="H98" t="n">
+        <v>50</v>
+      </c>
+      <c r="I98" t="n">
+        <v>60</v>
+      </c>
+      <c r="J98" t="n">
+        <v>8</v>
+      </c>
+      <c r="K98" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:55:17</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>100</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.6311428571428571</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>6</v>
+      </c>
+      <c r="G99" t="n">
+        <v>35</v>
+      </c>
+      <c r="H99" t="n">
+        <v>50</v>
+      </c>
+      <c r="I99" t="n">
+        <v>60</v>
+      </c>
+      <c r="J99" t="n">
+        <v>8</v>
+      </c>
+      <c r="K99" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:56:56</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>100</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>6</v>
+      </c>
+      <c r="G100" t="n">
+        <v>25</v>
+      </c>
+      <c r="H100" t="n">
+        <v>50</v>
+      </c>
+      <c r="I100" t="n">
+        <v>60</v>
+      </c>
+      <c r="J100" t="n">
+        <v>8</v>
+      </c>
+      <c r="K100" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-04-06 04:57:42</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>100</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>6</v>
+      </c>
+      <c r="G101" t="n">
+        <v>25</v>
+      </c>
+      <c r="H101" t="n">
+        <v>50</v>
+      </c>
+      <c r="I101" t="n">
+        <v>60</v>
+      </c>
+      <c r="J101" t="n">
+        <v>8</v>
+      </c>
+      <c r="K101" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-04-06 05:01:46</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>100</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>6</v>
+      </c>
+      <c r="G102" t="n">
+        <v>25</v>
+      </c>
+      <c r="H102" t="n">
+        <v>50</v>
+      </c>
+      <c r="I102" t="n">
+        <v>60</v>
+      </c>
+      <c r="J102" t="n">
+        <v>8</v>
+      </c>
+      <c r="K102" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-04-06 06:29:20</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.3495333333333333</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>6</v>
+      </c>
+      <c r="G103" t="n">
+        <v>30</v>
+      </c>
+      <c r="H103" t="n">
+        <v>50</v>
+      </c>
+      <c r="I103" t="n">
+        <v>60</v>
+      </c>
+      <c r="J103" t="n">
+        <v>8</v>
+      </c>
+      <c r="K103" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-04-06 06:31:01</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>6</v>
+      </c>
+      <c r="G104" t="n">
+        <v>30</v>
+      </c>
+      <c r="H104" t="n">
+        <v>50</v>
+      </c>
+      <c r="I104" t="n">
+        <v>60</v>
+      </c>
+      <c r="J104" t="n">
+        <v>8</v>
+      </c>
+      <c r="K104" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-04-06 06:32:39</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.4356666666666666</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>6</v>
+      </c>
+      <c r="G105" t="n">
+        <v>30</v>
+      </c>
+      <c r="H105" t="n">
+        <v>50</v>
+      </c>
+      <c r="I105" t="n">
+        <v>60</v>
+      </c>
+      <c r="J105" t="n">
+        <v>8</v>
+      </c>
+      <c r="K105" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-04-06 06:34:11</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.4677666666666667</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>6</v>
+      </c>
+      <c r="G106" t="n">
+        <v>30</v>
+      </c>
+      <c r="H106" t="n">
+        <v>50</v>
+      </c>
+      <c r="I106" t="n">
+        <v>60</v>
+      </c>
+      <c r="J106" t="n">
+        <v>8</v>
+      </c>
+      <c r="K106" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-04-06 06:49:39</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.3518444444444445</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>6</v>
+      </c>
+      <c r="G107" t="n">
+        <v>30</v>
+      </c>
+      <c r="H107" t="n">
+        <v>50</v>
+      </c>
+      <c r="I107" t="n">
+        <v>60</v>
+      </c>
+      <c r="J107" t="n">
+        <v>8</v>
+      </c>
+      <c r="K107" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-04-06 06:53:56</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.3363777777777778</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>6</v>
+      </c>
+      <c r="G108" t="n">
+        <v>30</v>
+      </c>
+      <c r="H108" t="n">
+        <v>50</v>
+      </c>
+      <c r="I108" t="n">
+        <v>60</v>
+      </c>
+      <c r="J108" t="n">
+        <v>8</v>
+      </c>
+      <c r="K108" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-04-06 06:58:37</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>6</v>
+      </c>
+      <c r="G109" t="n">
+        <v>30</v>
+      </c>
+      <c r="H109" t="n">
+        <v>50</v>
+      </c>
+      <c r="I109" t="n">
+        <v>60</v>
+      </c>
+      <c r="J109" t="n">
+        <v>8</v>
+      </c>
+      <c r="K109" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-04-06 07:02:56</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.4625555555555556</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>6</v>
+      </c>
+      <c r="G110" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" t="n">
+        <v>50</v>
+      </c>
+      <c r="I110" t="n">
+        <v>60</v>
+      </c>
+      <c r="J110" t="n">
+        <v>8</v>
+      </c>
+      <c r="K110" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-04-06 07:26:06</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>6</v>
+      </c>
+      <c r="G111" t="n">
+        <v>30</v>
+      </c>
+      <c r="H111" t="n">
+        <v>50</v>
+      </c>
+      <c r="I111" t="n">
+        <v>60</v>
+      </c>
+      <c r="J111" t="n">
+        <v>8</v>
+      </c>
+      <c r="K111" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-04-06 07:33:09</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>6</v>
+      </c>
+      <c r="G112" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" t="n">
+        <v>50</v>
+      </c>
+      <c r="I112" t="n">
+        <v>60</v>
+      </c>
+      <c r="J112" t="n">
+        <v>8</v>
+      </c>
+      <c r="K112" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-04-06 07:40:48</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.4494533333333333</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>6</v>
+      </c>
+      <c r="G113" t="n">
+        <v>30</v>
+      </c>
+      <c r="H113" t="n">
+        <v>50</v>
+      </c>
+      <c r="I113" t="n">
+        <v>60</v>
+      </c>
+      <c r="J113" t="n">
+        <v>8</v>
+      </c>
+      <c r="K113" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-04-06 07:48:09</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.4616333333333333</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>6</v>
+      </c>
+      <c r="G114" t="n">
+        <v>30</v>
+      </c>
+      <c r="H114" t="n">
+        <v>50</v>
+      </c>
+      <c r="I114" t="n">
+        <v>60</v>
+      </c>
+      <c r="J114" t="n">
+        <v>8</v>
+      </c>
+      <c r="K114" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-04-06 13:44:28</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>100</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>6</v>
+      </c>
+      <c r="G115" t="n">
+        <v>25</v>
+      </c>
+      <c r="H115" t="n">
+        <v>50</v>
+      </c>
+      <c r="I115" t="n">
+        <v>60</v>
+      </c>
+      <c r="J115" t="n">
+        <v>8</v>
+      </c>
+      <c r="K115" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-04-06 13:44:44</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>100</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>6</v>
+      </c>
+      <c r="G116" t="n">
+        <v>25</v>
+      </c>
+      <c r="H116" t="n">
+        <v>50</v>
+      </c>
+      <c r="I116" t="n">
+        <v>60</v>
+      </c>
+      <c r="J116" t="n">
+        <v>8</v>
+      </c>
+      <c r="K116" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-04-06 13:45:00</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>100</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.0472</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>6</v>
+      </c>
+      <c r="G117" t="n">
+        <v>25</v>
+      </c>
+      <c r="H117" t="n">
+        <v>50</v>
+      </c>
+      <c r="I117" t="n">
+        <v>60</v>
+      </c>
+      <c r="J117" t="n">
+        <v>8</v>
+      </c>
+      <c r="K117" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-04-06 13:45:16</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>100</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>6</v>
+      </c>
+      <c r="G118" t="n">
+        <v>25</v>
+      </c>
+      <c r="H118" t="n">
+        <v>50</v>
+      </c>
+      <c r="I118" t="n">
+        <v>60</v>
+      </c>
+      <c r="J118" t="n">
+        <v>8</v>
+      </c>
+      <c r="K118" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-04-06 13:46:37</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>100</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0.2421428571428571</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>6</v>
+      </c>
+      <c r="G119" t="n">
+        <v>28</v>
+      </c>
+      <c r="H119" t="n">
+        <v>50</v>
+      </c>
+      <c r="I119" t="n">
+        <v>60</v>
+      </c>
+      <c r="J119" t="n">
+        <v>8</v>
+      </c>
+      <c r="K119" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-04-06 13:46:53</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>100</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>6</v>
+      </c>
+      <c r="G120" t="n">
+        <v>28</v>
+      </c>
+      <c r="H120" t="n">
+        <v>50</v>
+      </c>
+      <c r="I120" t="n">
+        <v>60</v>
+      </c>
+      <c r="J120" t="n">
+        <v>8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-04-06 13:47:11</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>100</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0.2332142857142857</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>6</v>
+      </c>
+      <c r="G121" t="n">
+        <v>28</v>
+      </c>
+      <c r="H121" t="n">
+        <v>50</v>
+      </c>
+      <c r="I121" t="n">
+        <v>60</v>
+      </c>
+      <c r="J121" t="n">
+        <v>8</v>
+      </c>
+      <c r="K121" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-04-06 13:47:28</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>100</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0.2757142857142857</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>6</v>
+      </c>
+      <c r="G122" t="n">
+        <v>28</v>
+      </c>
+      <c r="H122" t="n">
+        <v>50</v>
+      </c>
+      <c r="I122" t="n">
+        <v>60</v>
+      </c>
+      <c r="J122" t="n">
+        <v>8</v>
+      </c>
+      <c r="K122" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-04-06 14:46:25</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>6</v>
+      </c>
+      <c r="G123" t="n">
+        <v>28</v>
+      </c>
+      <c r="H123" t="n">
+        <v>50</v>
+      </c>
+      <c r="I123" t="n">
+        <v>60</v>
+      </c>
+      <c r="J123" t="n">
+        <v>8</v>
+      </c>
+      <c r="K123" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-04-06 15:44:16</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>6</v>
+      </c>
+      <c r="G124" t="n">
+        <v>28</v>
+      </c>
+      <c r="H124" t="n">
+        <v>50</v>
+      </c>
+      <c r="I124" t="n">
+        <v>60</v>
+      </c>
+      <c r="J124" t="n">
+        <v>8</v>
+      </c>
+      <c r="K124" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04-06 15:45:38</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3214285714285715</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>6</v>
+      </c>
+      <c r="G125" t="n">
+        <v>28</v>
+      </c>
+      <c r="H125" t="n">
+        <v>50</v>
+      </c>
+      <c r="I125" t="n">
+        <v>60</v>
+      </c>
+      <c r="J125" t="n">
+        <v>8</v>
+      </c>
+      <c r="K125" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:02:21</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>6</v>
+      </c>
+      <c r="G126" t="n">
+        <v>38</v>
+      </c>
+      <c r="H126" t="n">
+        <v>50</v>
+      </c>
+      <c r="I126" t="n">
+        <v>60</v>
+      </c>
+      <c r="J126" t="n">
+        <v>8</v>
+      </c>
+      <c r="K126" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:03:54</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>6</v>
+      </c>
+      <c r="G127" t="n">
+        <v>25</v>
+      </c>
+      <c r="H127" t="n">
+        <v>50</v>
+      </c>
+      <c r="I127" t="n">
+        <v>60</v>
+      </c>
+      <c r="J127" t="n">
+        <v>8</v>
+      </c>
+      <c r="K127" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:04:41</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>6</v>
+      </c>
+      <c r="G128" t="n">
+        <v>25</v>
+      </c>
+      <c r="H128" t="n">
+        <v>50</v>
+      </c>
+      <c r="I128" t="n">
+        <v>60</v>
+      </c>
+      <c r="J128" t="n">
+        <v>8</v>
+      </c>
+      <c r="K128" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:05:18</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>6</v>
+      </c>
+      <c r="G129" t="n">
+        <v>50</v>
+      </c>
+      <c r="H129" t="n">
+        <v>50</v>
+      </c>
+      <c r="I129" t="n">
+        <v>60</v>
+      </c>
+      <c r="J129" t="n">
+        <v>8</v>
+      </c>
+      <c r="K129" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:05:56</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>6</v>
+      </c>
+      <c r="G130" t="n">
+        <v>50</v>
+      </c>
+      <c r="H130" t="n">
+        <v>50</v>
+      </c>
+      <c r="I130" t="n">
+        <v>60</v>
+      </c>
+      <c r="J130" t="n">
+        <v>8</v>
+      </c>
+      <c r="K130" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:08:06</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>6</v>
+      </c>
+      <c r="G131" t="n">
+        <v>50</v>
+      </c>
+      <c r="H131" t="n">
+        <v>50</v>
+      </c>
+      <c r="I131" t="n">
+        <v>60</v>
+      </c>
+      <c r="J131" t="n">
+        <v>8</v>
+      </c>
+      <c r="K131" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:26:03</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>6</v>
+      </c>
+      <c r="G132" t="n">
+        <v>50</v>
+      </c>
+      <c r="H132" t="n">
+        <v>50</v>
+      </c>
+      <c r="I132" t="n">
+        <v>60</v>
+      </c>
+      <c r="J132" t="n">
+        <v>8</v>
+      </c>
+      <c r="K132" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:26:47</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>6</v>
+      </c>
+      <c r="G133" t="n">
+        <v>25</v>
+      </c>
+      <c r="H133" t="n">
+        <v>50</v>
+      </c>
+      <c r="I133" t="n">
+        <v>60</v>
+      </c>
+      <c r="J133" t="n">
+        <v>8</v>
+      </c>
+      <c r="K133" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:27:13</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0.3214285714285715</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>6</v>
+      </c>
+      <c r="G134" t="n">
+        <v>28</v>
+      </c>
+      <c r="H134" t="n">
+        <v>50</v>
+      </c>
+      <c r="I134" t="n">
+        <v>60</v>
+      </c>
+      <c r="J134" t="n">
+        <v>8</v>
+      </c>
+      <c r="K134" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:32:31</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>6</v>
+      </c>
+      <c r="G135" t="n">
+        <v>28</v>
+      </c>
+      <c r="H135" t="n">
+        <v>50</v>
+      </c>
+      <c r="I135" t="n">
+        <v>60</v>
+      </c>
+      <c r="J135" t="n">
+        <v>8</v>
+      </c>
+      <c r="K135" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:43:38</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>6</v>
+      </c>
+      <c r="G136" t="n">
+        <v>50</v>
+      </c>
+      <c r="H136" t="n">
+        <v>50</v>
+      </c>
+      <c r="I136" t="n">
+        <v>60</v>
+      </c>
+      <c r="J136" t="n">
+        <v>8</v>
+      </c>
+      <c r="K136" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:57:31</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>6</v>
+      </c>
+      <c r="G137" t="n">
+        <v>28</v>
+      </c>
+      <c r="H137" t="n">
+        <v>50</v>
+      </c>
+      <c r="I137" t="n">
+        <v>60</v>
+      </c>
+      <c r="J137" t="n">
+        <v>8</v>
+      </c>
+      <c r="K137" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2025-04-06 19:59:55</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>6</v>
+      </c>
+      <c r="G138" t="n">
+        <v>50</v>
+      </c>
+      <c r="H138" t="n">
+        <v>50</v>
+      </c>
+      <c r="I138" t="n">
+        <v>60</v>
+      </c>
+      <c r="J138" t="n">
+        <v>8</v>
+      </c>
+      <c r="K138" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:00:30</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>6</v>
+      </c>
+      <c r="G139" t="n">
+        <v>30</v>
+      </c>
+      <c r="H139" t="n">
+        <v>50</v>
+      </c>
+      <c r="I139" t="n">
+        <v>60</v>
+      </c>
+      <c r="J139" t="n">
+        <v>8</v>
+      </c>
+      <c r="K139" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:00:53</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>6</v>
+      </c>
+      <c r="G140" t="n">
+        <v>30</v>
+      </c>
+      <c r="H140" t="n">
+        <v>50</v>
+      </c>
+      <c r="I140" t="n">
+        <v>60</v>
+      </c>
+      <c r="J140" t="n">
+        <v>8</v>
+      </c>
+      <c r="K140" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:01:56</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>6</v>
+      </c>
+      <c r="G141" t="n">
+        <v>50</v>
+      </c>
+      <c r="H141" t="n">
+        <v>50</v>
+      </c>
+      <c r="I141" t="n">
+        <v>60</v>
+      </c>
+      <c r="J141" t="n">
+        <v>8</v>
+      </c>
+      <c r="K141" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:03:10</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>6</v>
+      </c>
+      <c r="G142" t="n">
+        <v>30</v>
+      </c>
+      <c r="H142" t="n">
+        <v>50</v>
+      </c>
+      <c r="I142" t="n">
+        <v>60</v>
+      </c>
+      <c r="J142" t="n">
+        <v>8</v>
+      </c>
+      <c r="K142" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:21:09</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>6</v>
+      </c>
+      <c r="G143" t="n">
+        <v>49</v>
+      </c>
+      <c r="H143" t="n">
+        <v>50</v>
+      </c>
+      <c r="I143" t="n">
+        <v>60</v>
+      </c>
+      <c r="J143" t="n">
+        <v>8</v>
+      </c>
+      <c r="K143" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:21:38</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>6</v>
+      </c>
+      <c r="G144" t="n">
+        <v>50</v>
+      </c>
+      <c r="H144" t="n">
+        <v>50</v>
+      </c>
+      <c r="I144" t="n">
+        <v>60</v>
+      </c>
+      <c r="J144" t="n">
+        <v>8</v>
+      </c>
+      <c r="K144" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:26:46</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>6</v>
+      </c>
+      <c r="G145" t="n">
+        <v>10</v>
+      </c>
+      <c r="H145" t="n">
+        <v>50</v>
+      </c>
+      <c r="I145" t="n">
+        <v>60</v>
+      </c>
+      <c r="J145" t="n">
+        <v>8</v>
+      </c>
+      <c r="K145" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:55:03</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>100</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>6</v>
+      </c>
+      <c r="G146" t="n">
+        <v>25</v>
+      </c>
+      <c r="H146" t="n">
+        <v>50</v>
+      </c>
+      <c r="I146" t="n">
+        <v>60</v>
+      </c>
+      <c r="J146" t="n">
+        <v>8</v>
+      </c>
+      <c r="K146" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:55:19</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>100</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.1944</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>6</v>
+      </c>
+      <c r="G147" t="n">
+        <v>25</v>
+      </c>
+      <c r="H147" t="n">
+        <v>50</v>
+      </c>
+      <c r="I147" t="n">
+        <v>60</v>
+      </c>
+      <c r="J147" t="n">
+        <v>8</v>
+      </c>
+      <c r="K147" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:55:40</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>100</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>6</v>
+      </c>
+      <c r="G148" t="n">
+        <v>25</v>
+      </c>
+      <c r="H148" t="n">
+        <v>50</v>
+      </c>
+      <c r="I148" t="n">
+        <v>60</v>
+      </c>
+      <c r="J148" t="n">
+        <v>8</v>
+      </c>
+      <c r="K148" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:55:56</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>100</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>6</v>
+      </c>
+      <c r="G149" t="n">
+        <v>25</v>
+      </c>
+      <c r="H149" t="n">
+        <v>50</v>
+      </c>
+      <c r="I149" t="n">
+        <v>60</v>
+      </c>
+      <c r="J149" t="n">
+        <v>8</v>
+      </c>
+      <c r="K149" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:57:23</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>100</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0.5073333333333333</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>6</v>
+      </c>
+      <c r="G150" t="n">
+        <v>30</v>
+      </c>
+      <c r="H150" t="n">
+        <v>50</v>
+      </c>
+      <c r="I150" t="n">
+        <v>60</v>
+      </c>
+      <c r="J150" t="n">
+        <v>8</v>
+      </c>
+      <c r="K150" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:57:40</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>100</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.4913333333333333</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>6</v>
+      </c>
+      <c r="G151" t="n">
+        <v>30</v>
+      </c>
+      <c r="H151" t="n">
+        <v>50</v>
+      </c>
+      <c r="I151" t="n">
+        <v>60</v>
+      </c>
+      <c r="J151" t="n">
+        <v>8</v>
+      </c>
+      <c r="K151" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:57:59</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>100</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>6</v>
+      </c>
+      <c r="G152" t="n">
+        <v>30</v>
+      </c>
+      <c r="H152" t="n">
+        <v>50</v>
+      </c>
+      <c r="I152" t="n">
+        <v>60</v>
+      </c>
+      <c r="J152" t="n">
+        <v>8</v>
+      </c>
+      <c r="K152" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2025-04-06 20:58:17</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>100</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>6</v>
+      </c>
+      <c r="G153" t="n">
+        <v>30</v>
+      </c>
+      <c r="H153" t="n">
+        <v>50</v>
+      </c>
+      <c r="I153" t="n">
+        <v>60</v>
+      </c>
+      <c r="J153" t="n">
+        <v>8</v>
+      </c>
+      <c r="K153" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2025-04-06 21:01:55</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>100</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>6</v>
+      </c>
+      <c r="G154" t="n">
+        <v>40</v>
+      </c>
+      <c r="H154" t="n">
+        <v>50</v>
+      </c>
+      <c r="I154" t="n">
+        <v>60</v>
+      </c>
+      <c r="J154" t="n">
+        <v>8</v>
+      </c>
+      <c r="K154" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2025-04-06 21:02:17</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>100</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>6</v>
+      </c>
+      <c r="G155" t="n">
+        <v>40</v>
+      </c>
+      <c r="H155" t="n">
+        <v>50</v>
+      </c>
+      <c r="I155" t="n">
+        <v>60</v>
+      </c>
+      <c r="J155" t="n">
+        <v>8</v>
+      </c>
+      <c r="K155" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2025-04-06 21:02:41</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>100</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>6</v>
+      </c>
+      <c r="G156" t="n">
+        <v>40</v>
+      </c>
+      <c r="H156" t="n">
+        <v>50</v>
+      </c>
+      <c r="I156" t="n">
+        <v>60</v>
+      </c>
+      <c r="J156" t="n">
+        <v>8</v>
+      </c>
+      <c r="K156" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2025-04-06 21:03:02</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>100</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0.99625</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>6</v>
+      </c>
+      <c r="G157" t="n">
+        <v>40</v>
+      </c>
+      <c r="H157" t="n">
+        <v>50</v>
+      </c>
+      <c r="I157" t="n">
+        <v>60</v>
+      </c>
+      <c r="J157" t="n">
+        <v>8</v>
+      </c>
+      <c r="K157" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2025-04-06 21:08:57</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0.2142112856684835</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>6</v>
+      </c>
+      <c r="G158" t="n">
+        <v>25</v>
+      </c>
+      <c r="H158" t="n">
+        <v>50</v>
+      </c>
+      <c r="I158" t="n">
+        <v>60</v>
+      </c>
+      <c r="J158" t="n">
+        <v>8</v>
+      </c>
+      <c r="K158" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2025-04-06 21:14:32</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0.522905475292783</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>6</v>
+      </c>
+      <c r="G159" t="n">
+        <v>30</v>
+      </c>
+      <c r="H159" t="n">
+        <v>50</v>
+      </c>
+      <c r="I159" t="n">
+        <v>60</v>
+      </c>
+      <c r="J159" t="n">
+        <v>8</v>
+      </c>
+      <c r="K159" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2025-04-06 21:52:38</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0.9504586747417172</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>6</v>
+      </c>
+      <c r="G160" t="n">
+        <v>45</v>
+      </c>
+      <c r="H160" t="n">
+        <v>50</v>
+      </c>
+      <c r="I160" t="n">
+        <v>60</v>
+      </c>
+      <c r="J160" t="n">
+        <v>8</v>
+      </c>
+      <c r="K160" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:10:01</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0.9836479499819647</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>6</v>
+      </c>
+      <c r="G161" t="n">
+        <v>50</v>
+      </c>
+      <c r="H161" t="n">
+        <v>50</v>
+      </c>
+      <c r="I161" t="n">
+        <v>60</v>
+      </c>
+      <c r="J161" t="n">
+        <v>8</v>
+      </c>
+      <c r="K161" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:12:08</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0.2368146841936518</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>6</v>
+      </c>
+      <c r="G162" t="n">
+        <v>25</v>
+      </c>
+      <c r="H162" t="n">
+        <v>50</v>
+      </c>
+      <c r="I162" t="n">
+        <v>60</v>
+      </c>
+      <c r="J162" t="n">
+        <v>8</v>
+      </c>
+      <c r="K162" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:13:47</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0.4588769143505388</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>6</v>
+      </c>
+      <c r="G163" t="n">
+        <v>30</v>
+      </c>
+      <c r="H163" t="n">
+        <v>50</v>
+      </c>
+      <c r="I163" t="n">
+        <v>60</v>
+      </c>
+      <c r="J163" t="n">
+        <v>8</v>
+      </c>
+      <c r="K163" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:15:46</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.6823771663902076</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>6</v>
+      </c>
+      <c r="G164" t="n">
+        <v>35</v>
+      </c>
+      <c r="H164" t="n">
+        <v>50</v>
+      </c>
+      <c r="I164" t="n">
+        <v>60</v>
+      </c>
+      <c r="J164" t="n">
+        <v>8</v>
+      </c>
+      <c r="K164" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:18:40</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0.8143189609869623</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>6</v>
+      </c>
+      <c r="G165" t="n">
+        <v>40</v>
+      </c>
+      <c r="H165" t="n">
+        <v>50</v>
+      </c>
+      <c r="I165" t="n">
+        <v>60</v>
+      </c>
+      <c r="J165" t="n">
+        <v>8</v>
+      </c>
+      <c r="K165" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:21:42</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0.9093119757272889</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>6</v>
+      </c>
+      <c r="G166" t="n">
+        <v>45</v>
+      </c>
+      <c r="H166" t="n">
+        <v>50</v>
+      </c>
+      <c r="I166" t="n">
+        <v>60</v>
+      </c>
+      <c r="J166" t="n">
+        <v>8</v>
+      </c>
+      <c r="K166" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:24:59</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0.9657664511220997</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>6</v>
+      </c>
+      <c r="G167" t="n">
+        <v>50</v>
+      </c>
+      <c r="H167" t="n">
+        <v>50</v>
+      </c>
+      <c r="I167" t="n">
+        <v>60</v>
+      </c>
+      <c r="J167" t="n">
+        <v>8</v>
+      </c>
+      <c r="K167" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:26:27</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0.2715006406149904</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>6</v>
+      </c>
+      <c r="G168" t="n">
+        <v>25</v>
+      </c>
+      <c r="H168" t="n">
+        <v>50</v>
+      </c>
+      <c r="I168" t="n">
+        <v>60</v>
+      </c>
+      <c r="J168" t="n">
+        <v>8</v>
+      </c>
+      <c r="K168" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:28:16</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0.5906709819492175</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>6</v>
+      </c>
+      <c r="G169" t="n">
+        <v>30</v>
+      </c>
+      <c r="H169" t="n">
+        <v>50</v>
+      </c>
+      <c r="I169" t="n">
+        <v>60</v>
+      </c>
+      <c r="J169" t="n">
+        <v>8</v>
+      </c>
+      <c r="K169" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:30:24</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0.9315527310202679</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>6</v>
+      </c>
+      <c r="G170" t="n">
+        <v>35</v>
+      </c>
+      <c r="H170" t="n">
+        <v>50</v>
+      </c>
+      <c r="I170" t="n">
+        <v>60</v>
+      </c>
+      <c r="J170" t="n">
+        <v>8</v>
+      </c>
+      <c r="K170" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:32:57</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0.999725</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>6</v>
+      </c>
+      <c r="G171" t="n">
+        <v>40</v>
+      </c>
+      <c r="H171" t="n">
+        <v>50</v>
+      </c>
+      <c r="I171" t="n">
+        <v>60</v>
+      </c>
+      <c r="J171" t="n">
+        <v>8</v>
+      </c>
+      <c r="K171" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:36:03</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0.9999331372024606</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>6</v>
+      </c>
+      <c r="G172" t="n">
+        <v>45</v>
+      </c>
+      <c r="H172" t="n">
+        <v>50</v>
+      </c>
+      <c r="I172" t="n">
+        <v>60</v>
+      </c>
+      <c r="J172" t="n">
+        <v>8</v>
+      </c>
+      <c r="K172" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:39:26</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>0.9999799803807732</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>6</v>
+      </c>
+      <c r="G173" t="n">
+        <v>50</v>
+      </c>
+      <c r="H173" t="n">
+        <v>50</v>
+      </c>
+      <c r="I173" t="n">
+        <v>60</v>
+      </c>
+      <c r="J173" t="n">
+        <v>8</v>
+      </c>
+      <c r="K173" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:40:48</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0.2858287912792561</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>6</v>
+      </c>
+      <c r="G174" t="n">
+        <v>25</v>
+      </c>
+      <c r="H174" t="n">
+        <v>50</v>
+      </c>
+      <c r="I174" t="n">
+        <v>60</v>
+      </c>
+      <c r="J174" t="n">
+        <v>8</v>
+      </c>
+      <c r="K174" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:42:32</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0.6057043617660811</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>6</v>
+      </c>
+      <c r="G175" t="n">
+        <v>30</v>
+      </c>
+      <c r="H175" t="n">
+        <v>50</v>
+      </c>
+      <c r="I175" t="n">
+        <v>60</v>
+      </c>
+      <c r="J175" t="n">
+        <v>8</v>
+      </c>
+      <c r="K175" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:44:59</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0.9020668727814039</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>6</v>
+      </c>
+      <c r="G176" t="n">
+        <v>35</v>
+      </c>
+      <c r="H176" t="n">
+        <v>50</v>
+      </c>
+      <c r="I176" t="n">
+        <v>60</v>
+      </c>
+      <c r="J176" t="n">
+        <v>8</v>
+      </c>
+      <c r="K176" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:47:46</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0.996793747808226</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>6</v>
+      </c>
+      <c r="G177" t="n">
+        <v>40</v>
+      </c>
+      <c r="H177" t="n">
+        <v>50</v>
+      </c>
+      <c r="I177" t="n">
+        <v>60</v>
+      </c>
+      <c r="J177" t="n">
+        <v>8</v>
+      </c>
+      <c r="K177" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:51:10</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0.9999777560281163</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>6</v>
+      </c>
+      <c r="G178" t="n">
+        <v>45</v>
+      </c>
+      <c r="H178" t="n">
+        <v>50</v>
+      </c>
+      <c r="I178" t="n">
+        <v>60</v>
+      </c>
+      <c r="J178" t="n">
+        <v>8</v>
+      </c>
+      <c r="K178" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2025-04-06 22:54:59</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0.9999599214460342</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>6</v>
+      </c>
+      <c r="G179" t="n">
+        <v>50</v>
+      </c>
+      <c r="H179" t="n">
+        <v>50</v>
+      </c>
+      <c r="I179" t="n">
+        <v>60</v>
+      </c>
+      <c r="J179" t="n">
+        <v>8</v>
+      </c>
+      <c r="K179" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:05:52</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>100</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>6</v>
+      </c>
+      <c r="G180" t="n">
+        <v>25</v>
+      </c>
+      <c r="H180" t="n">
+        <v>50</v>
+      </c>
+      <c r="I180" t="n">
+        <v>60</v>
+      </c>
+      <c r="J180" t="n">
+        <v>8</v>
+      </c>
+      <c r="K180" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:06:11</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>100</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>6</v>
+      </c>
+      <c r="G181" t="n">
+        <v>25</v>
+      </c>
+      <c r="H181" t="n">
+        <v>50</v>
+      </c>
+      <c r="I181" t="n">
+        <v>60</v>
+      </c>
+      <c r="J181" t="n">
+        <v>8</v>
+      </c>
+      <c r="K181" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:06:29</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>100</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>6</v>
+      </c>
+      <c r="G182" t="n">
+        <v>25</v>
+      </c>
+      <c r="H182" t="n">
+        <v>50</v>
+      </c>
+      <c r="I182" t="n">
+        <v>60</v>
+      </c>
+      <c r="J182" t="n">
+        <v>8</v>
+      </c>
+      <c r="K182" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:07:10</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>100</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>6</v>
+      </c>
+      <c r="G183" t="n">
+        <v>25</v>
+      </c>
+      <c r="H183" t="n">
+        <v>50</v>
+      </c>
+      <c r="I183" t="n">
+        <v>60</v>
+      </c>
+      <c r="J183" t="n">
+        <v>8</v>
+      </c>
+      <c r="K183" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:11:36</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>100</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0.3346666666666667</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>6</v>
+      </c>
+      <c r="G184" t="n">
+        <v>30</v>
+      </c>
+      <c r="H184" t="n">
+        <v>50</v>
+      </c>
+      <c r="I184" t="n">
+        <v>60</v>
+      </c>
+      <c r="J184" t="n">
+        <v>8</v>
+      </c>
+      <c r="K184" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:11:55</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>100</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0.4113333333333333</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>6</v>
+      </c>
+      <c r="G185" t="n">
+        <v>30</v>
+      </c>
+      <c r="H185" t="n">
+        <v>50</v>
+      </c>
+      <c r="I185" t="n">
+        <v>60</v>
+      </c>
+      <c r="J185" t="n">
+        <v>8</v>
+      </c>
+      <c r="K185" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:12:13</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>100</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0.4673333333333333</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>6</v>
+      </c>
+      <c r="G186" t="n">
+        <v>30</v>
+      </c>
+      <c r="H186" t="n">
+        <v>50</v>
+      </c>
+      <c r="I186" t="n">
+        <v>60</v>
+      </c>
+      <c r="J186" t="n">
+        <v>8</v>
+      </c>
+      <c r="K186" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:12:58</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>100</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>0.4383333333333334</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>6</v>
+      </c>
+      <c r="G187" t="n">
+        <v>30</v>
+      </c>
+      <c r="H187" t="n">
+        <v>50</v>
+      </c>
+      <c r="I187" t="n">
+        <v>60</v>
+      </c>
+      <c r="J187" t="n">
+        <v>8</v>
+      </c>
+      <c r="K187" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:15:11</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>100</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0.7655</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>6</v>
+      </c>
+      <c r="G188" t="n">
+        <v>40</v>
+      </c>
+      <c r="H188" t="n">
+        <v>50</v>
+      </c>
+      <c r="I188" t="n">
+        <v>60</v>
+      </c>
+      <c r="J188" t="n">
+        <v>8</v>
+      </c>
+      <c r="K188" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:15:36</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>100</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>6</v>
+      </c>
+      <c r="G189" t="n">
+        <v>40</v>
+      </c>
+      <c r="H189" t="n">
+        <v>50</v>
+      </c>
+      <c r="I189" t="n">
+        <v>60</v>
+      </c>
+      <c r="J189" t="n">
+        <v>8</v>
+      </c>
+      <c r="K189" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:16:01</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>100</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>0.99725</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>6</v>
+      </c>
+      <c r="G190" t="n">
+        <v>40</v>
+      </c>
+      <c r="H190" t="n">
+        <v>50</v>
+      </c>
+      <c r="I190" t="n">
+        <v>60</v>
+      </c>
+      <c r="J190" t="n">
+        <v>8</v>
+      </c>
+      <c r="K190" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:17:36</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>100</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>0.80525</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>6</v>
+      </c>
+      <c r="G191" t="n">
+        <v>40</v>
+      </c>
+      <c r="H191" t="n">
+        <v>50</v>
+      </c>
+      <c r="I191" t="n">
+        <v>60</v>
+      </c>
+      <c r="J191" t="n">
+        <v>8</v>
+      </c>
+      <c r="K191" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:19:18</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>100</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0.5928571428571429</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>6</v>
+      </c>
+      <c r="G192" t="n">
+        <v>35</v>
+      </c>
+      <c r="H192" t="n">
+        <v>50</v>
+      </c>
+      <c r="I192" t="n">
+        <v>60</v>
+      </c>
+      <c r="J192" t="n">
+        <v>8</v>
+      </c>
+      <c r="K192" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:19:40</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>100</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0.9077142857142857</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>6</v>
+      </c>
+      <c r="G193" t="n">
+        <v>35</v>
+      </c>
+      <c r="H193" t="n">
+        <v>50</v>
+      </c>
+      <c r="I193" t="n">
+        <v>60</v>
+      </c>
+      <c r="J193" t="n">
+        <v>8</v>
+      </c>
+      <c r="K193" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:20:00</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>100</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>6</v>
+      </c>
+      <c r="G194" t="n">
+        <v>35</v>
+      </c>
+      <c r="H194" t="n">
+        <v>50</v>
+      </c>
+      <c r="I194" t="n">
+        <v>60</v>
+      </c>
+      <c r="J194" t="n">
+        <v>8</v>
+      </c>
+      <c r="K194" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2025-04-07 03:20:50</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>100</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>0.6588571428571428</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>6</v>
+      </c>
+      <c r="G195" t="n">
+        <v>35</v>
+      </c>
+      <c r="H195" t="n">
+        <v>50</v>
+      </c>
+      <c r="I195" t="n">
+        <v>60</v>
+      </c>
+      <c r="J195" t="n">
+        <v>8</v>
+      </c>
+      <c r="K195" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:55:41</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>10</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0.5693069306930693</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>6</v>
+      </c>
+      <c r="G196" t="n">
+        <v>25</v>
+      </c>
+      <c r="H196" t="n">
+        <v>50</v>
+      </c>
+      <c r="I196" t="n">
+        <v>60</v>
+      </c>
+      <c r="J196" t="n">
+        <v>8</v>
+      </c>
+      <c r="K196" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:55:51</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>10</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>6</v>
+      </c>
+      <c r="G197" t="n">
+        <v>25</v>
+      </c>
+      <c r="H197" t="n">
+        <v>50</v>
+      </c>
+      <c r="I197" t="n">
+        <v>60</v>
+      </c>
+      <c r="J197" t="n">
+        <v>8</v>
+      </c>
+      <c r="K197" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:56:00</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>10</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>6</v>
+      </c>
+      <c r="G198" t="n">
+        <v>25</v>
+      </c>
+      <c r="H198" t="n">
+        <v>50</v>
+      </c>
+      <c r="I198" t="n">
+        <v>60</v>
+      </c>
+      <c r="J198" t="n">
+        <v>8</v>
+      </c>
+      <c r="K198" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:56:11</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>10</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0.1910112359550562</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>6</v>
+      </c>
+      <c r="G199" t="n">
+        <v>25</v>
+      </c>
+      <c r="H199" t="n">
+        <v>50</v>
+      </c>
+      <c r="I199" t="n">
+        <v>60</v>
+      </c>
+      <c r="J199" t="n">
+        <v>8</v>
+      </c>
+      <c r="K199" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:56:21</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>10</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0.5826446280991735</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>6</v>
+      </c>
+      <c r="G200" t="n">
+        <v>30</v>
+      </c>
+      <c r="H200" t="n">
+        <v>50</v>
+      </c>
+      <c r="I200" t="n">
+        <v>60</v>
+      </c>
+      <c r="J200" t="n">
+        <v>8</v>
+      </c>
+      <c r="K200" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:56:31</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>10</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>6</v>
+      </c>
+      <c r="G201" t="n">
+        <v>30</v>
+      </c>
+      <c r="H201" t="n">
+        <v>50</v>
+      </c>
+      <c r="I201" t="n">
+        <v>60</v>
+      </c>
+      <c r="J201" t="n">
+        <v>8</v>
+      </c>
+      <c r="K201" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:56:41</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>10</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>0.6652892561983471</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>6</v>
+      </c>
+      <c r="G202" t="n">
+        <v>30</v>
+      </c>
+      <c r="H202" t="n">
+        <v>50</v>
+      </c>
+      <c r="I202" t="n">
+        <v>60</v>
+      </c>
+      <c r="J202" t="n">
+        <v>8</v>
+      </c>
+      <c r="K202" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:56:53</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>10</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>0.6531365313653137</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>6</v>
+      </c>
+      <c r="G203" t="n">
+        <v>30</v>
+      </c>
+      <c r="H203" t="n">
+        <v>50</v>
+      </c>
+      <c r="I203" t="n">
+        <v>60</v>
+      </c>
+      <c r="J203" t="n">
+        <v>8</v>
+      </c>
+      <c r="K203" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:57:03</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>10</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>0.7242990654205608</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>6</v>
+      </c>
+      <c r="G204" t="n">
+        <v>35</v>
+      </c>
+      <c r="H204" t="n">
+        <v>50</v>
+      </c>
+      <c r="I204" t="n">
+        <v>60</v>
+      </c>
+      <c r="J204" t="n">
+        <v>8</v>
+      </c>
+      <c r="K204" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:57:13</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>10</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>0.9722222222222222</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>6</v>
+      </c>
+      <c r="G205" t="n">
+        <v>35</v>
+      </c>
+      <c r="H205" t="n">
+        <v>50</v>
+      </c>
+      <c r="I205" t="n">
+        <v>60</v>
+      </c>
+      <c r="J205" t="n">
+        <v>8</v>
+      </c>
+      <c r="K205" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:57:23</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>10</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>0.9574468085106383</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>6</v>
+      </c>
+      <c r="G206" t="n">
+        <v>35</v>
+      </c>
+      <c r="H206" t="n">
+        <v>50</v>
+      </c>
+      <c r="I206" t="n">
+        <v>60</v>
+      </c>
+      <c r="J206" t="n">
+        <v>8</v>
+      </c>
+      <c r="K206" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:57:35</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>10</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>0.8297872340425532</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>6</v>
+      </c>
+      <c r="G207" t="n">
+        <v>35</v>
+      </c>
+      <c r="H207" t="n">
+        <v>50</v>
+      </c>
+      <c r="I207" t="n">
+        <v>60</v>
+      </c>
+      <c r="J207" t="n">
+        <v>8</v>
+      </c>
+      <c r="K207" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:57:45</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>10</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>0.8836565096952909</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>6</v>
+      </c>
+      <c r="G208" t="n">
+        <v>40</v>
+      </c>
+      <c r="H208" t="n">
+        <v>50</v>
+      </c>
+      <c r="I208" t="n">
+        <v>60</v>
+      </c>
+      <c r="J208" t="n">
+        <v>8</v>
+      </c>
+      <c r="K208" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:57:56</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>10</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>0.997229916897507</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>6</v>
+      </c>
+      <c r="G209" t="n">
+        <v>40</v>
+      </c>
+      <c r="H209" t="n">
+        <v>50</v>
+      </c>
+      <c r="I209" t="n">
+        <v>60</v>
+      </c>
+      <c r="J209" t="n">
+        <v>8</v>
+      </c>
+      <c r="K209" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:58:06</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>10</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>6</v>
+      </c>
+      <c r="G210" t="n">
+        <v>40</v>
+      </c>
+      <c r="H210" t="n">
+        <v>50</v>
+      </c>
+      <c r="I210" t="n">
+        <v>60</v>
+      </c>
+      <c r="J210" t="n">
+        <v>8</v>
+      </c>
+      <c r="K210" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2025-04-07 04:58:27</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>10</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>0.922360248447205</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>6</v>
+      </c>
+      <c r="G211" t="n">
+        <v>40</v>
+      </c>
+      <c r="H211" t="n">
+        <v>50</v>
+      </c>
+      <c r="I211" t="n">
+        <v>60</v>
+      </c>
+      <c r="J211" t="n">
+        <v>8</v>
+      </c>
+      <c r="K211" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:03:45</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>0.429128277817151</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>6</v>
+      </c>
+      <c r="G212" t="n">
+        <v>25</v>
+      </c>
+      <c r="H212" t="n">
+        <v>50</v>
+      </c>
+      <c r="I212" t="n">
+        <v>60</v>
+      </c>
+      <c r="J212" t="n">
+        <v>8</v>
+      </c>
+      <c r="K212" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:05:19</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>0.5738065326633166</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>6</v>
+      </c>
+      <c r="G213" t="n">
+        <v>25</v>
+      </c>
+      <c r="H213" t="n">
+        <v>50</v>
+      </c>
+      <c r="I213" t="n">
+        <v>60</v>
+      </c>
+      <c r="J213" t="n">
+        <v>8</v>
+      </c>
+      <c r="K213" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:06:38</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>0.6067670537010159</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>6</v>
+      </c>
+      <c r="G214" t="n">
+        <v>25</v>
+      </c>
+      <c r="H214" t="n">
+        <v>50</v>
+      </c>
+      <c r="I214" t="n">
+        <v>60</v>
+      </c>
+      <c r="J214" t="n">
+        <v>8</v>
+      </c>
+      <c r="K214" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:10:36</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>A2C</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>0.2766211906449327</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>6</v>
+      </c>
+      <c r="G215" t="n">
+        <v>25</v>
+      </c>
+      <c r="H215" t="n">
+        <v>50</v>
+      </c>
+      <c r="I215" t="n">
+        <v>60</v>
+      </c>
+      <c r="J215" t="n">
+        <v>8</v>
+      </c>
+      <c r="K215" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:12:11</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>0.6296613005167863</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>6</v>
+      </c>
+      <c r="G216" t="n">
+        <v>30</v>
+      </c>
+      <c r="H216" t="n">
+        <v>50</v>
+      </c>
+      <c r="I216" t="n">
+        <v>60</v>
+      </c>
+      <c r="J216" t="n">
+        <v>8</v>
+      </c>
+      <c r="K216" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:13:55</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>0.7946239357549169</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>6</v>
+      </c>
+      <c r="G217" t="n">
+        <v>30</v>
+      </c>
+      <c r="H217" t="n">
+        <v>50</v>
+      </c>
+      <c r="I217" t="n">
+        <v>60</v>
+      </c>
+      <c r="J217" t="n">
+        <v>8</v>
+      </c>
+      <c r="K217" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:15:32</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>0.7817867478483106</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>6</v>
+      </c>
+      <c r="G218" t="n">
+        <v>30</v>
+      </c>
+      <c r="H218" t="n">
+        <v>50</v>
+      </c>
+      <c r="I218" t="n">
+        <v>60</v>
+      </c>
+      <c r="J218" t="n">
+        <v>8</v>
+      </c>
+      <c r="K218" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:36:50</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>0.7820827943078913</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>6</v>
+      </c>
+      <c r="G219" t="n">
+        <v>35</v>
+      </c>
+      <c r="H219" t="n">
+        <v>50</v>
+      </c>
+      <c r="I219" t="n">
+        <v>60</v>
+      </c>
+      <c r="J219" t="n">
+        <v>8</v>
+      </c>
+      <c r="K219" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:38:54</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>0.9554937867887509</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>6</v>
+      </c>
+      <c r="G220" t="n">
+        <v>35</v>
+      </c>
+      <c r="H220" t="n">
+        <v>50</v>
+      </c>
+      <c r="I220" t="n">
+        <v>60</v>
+      </c>
+      <c r="J220" t="n">
+        <v>8</v>
+      </c>
+      <c r="K220" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:40:49</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>0.9466387906079126</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>6</v>
+      </c>
+      <c r="G221" t="n">
+        <v>35</v>
+      </c>
+      <c r="H221" t="n">
+        <v>50</v>
+      </c>
+      <c r="I221" t="n">
+        <v>60</v>
+      </c>
+      <c r="J221" t="n">
+        <v>8</v>
+      </c>
+      <c r="K221" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:43:02</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>0.888134261338123</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>6</v>
+      </c>
+      <c r="G222" t="n">
+        <v>40</v>
+      </c>
+      <c r="H222" t="n">
+        <v>50</v>
+      </c>
+      <c r="I222" t="n">
+        <v>60</v>
+      </c>
+      <c r="J222" t="n">
+        <v>8</v>
+      </c>
+      <c r="K222" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:45:28</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>0.9959172180768689</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>6</v>
+      </c>
+      <c r="G223" t="n">
+        <v>40</v>
+      </c>
+      <c r="H223" t="n">
+        <v>50</v>
+      </c>
+      <c r="I223" t="n">
+        <v>60</v>
+      </c>
+      <c r="J223" t="n">
+        <v>8</v>
+      </c>
+      <c r="K223" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:47:42</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>0.9931060236118692</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>6</v>
+      </c>
+      <c r="G224" t="n">
+        <v>40</v>
+      </c>
+      <c r="H224" t="n">
+        <v>50</v>
+      </c>
+      <c r="I224" t="n">
+        <v>60</v>
+      </c>
+      <c r="J224" t="n">
+        <v>8</v>
+      </c>
+      <c r="K224" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:53:02</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>0.7977750817825343</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>6</v>
+      </c>
+      <c r="G225" t="n">
+        <v>35</v>
+      </c>
+      <c r="H225" t="n">
+        <v>50</v>
+      </c>
+      <c r="I225" t="n">
+        <v>60</v>
+      </c>
+      <c r="J225" t="n">
+        <v>8</v>
+      </c>
+      <c r="K225" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2025-04-07 05:58:52</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>0.9580471847310383</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>6</v>
+      </c>
+      <c r="G226" t="n">
+        <v>35</v>
+      </c>
+      <c r="H226" t="n">
+        <v>50</v>
+      </c>
+      <c r="I226" t="n">
+        <v>60</v>
+      </c>
+      <c r="J226" t="n">
+        <v>8</v>
+      </c>
+      <c r="K226" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2025-04-07 06:04:20</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>0.9401831835742501</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>6</v>
+      </c>
+      <c r="G227" t="n">
+        <v>35</v>
+      </c>
+      <c r="H227" t="n">
+        <v>50</v>
+      </c>
+      <c r="I227" t="n">
+        <v>60</v>
+      </c>
+      <c r="J227" t="n">
+        <v>8</v>
+      </c>
+      <c r="K227" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2025-04-07 06:10:39</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>0.8932356504402408</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>6</v>
+      </c>
+      <c r="G228" t="n">
+        <v>40</v>
+      </c>
+      <c r="H228" t="n">
+        <v>50</v>
+      </c>
+      <c r="I228" t="n">
+        <v>60</v>
+      </c>
+      <c r="J228" t="n">
+        <v>8</v>
+      </c>
+      <c r="K228" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2025-04-07 06:17:35</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>0.9956744300258779</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>6</v>
+      </c>
+      <c r="G229" t="n">
+        <v>40</v>
+      </c>
+      <c r="H229" t="n">
+        <v>50</v>
+      </c>
+      <c r="I229" t="n">
+        <v>60</v>
+      </c>
+      <c r="J229" t="n">
+        <v>8</v>
+      </c>
+      <c r="K229" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2025-04-07 06:24:10</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>0.9936545983258545</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>6</v>
+      </c>
+      <c r="G230" t="n">
+        <v>40</v>
+      </c>
+      <c r="H230" t="n">
+        <v>50</v>
+      </c>
+      <c r="I230" t="n">
+        <v>60</v>
+      </c>
+      <c r="J230" t="n">
+        <v>8</v>
+      </c>
+      <c r="K230" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2025-04-07 06:33:00</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>0.8001398076350503</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>6</v>
+      </c>
+      <c r="G231" t="n">
+        <v>35</v>
+      </c>
+      <c r="H231" t="n">
+        <v>50</v>
+      </c>
+      <c r="I231" t="n">
+        <v>60</v>
+      </c>
+      <c r="J231" t="n">
+        <v>8</v>
+      </c>
+      <c r="K231" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2025-04-07 06:42:44</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>0.9564716750370814</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>6</v>
+      </c>
+      <c r="G232" t="n">
+        <v>35</v>
+      </c>
+      <c r="H232" t="n">
+        <v>50</v>
+      </c>
+      <c r="I232" t="n">
+        <v>60</v>
+      </c>
+      <c r="J232" t="n">
+        <v>8</v>
+      </c>
+      <c r="K232" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2025-04-07 06:51:47</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>0.9452286333608588</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>6</v>
+      </c>
+      <c r="G233" t="n">
+        <v>35</v>
+      </c>
+      <c r="H233" t="n">
+        <v>50</v>
+      </c>
+      <c r="I233" t="n">
+        <v>60</v>
+      </c>
+      <c r="J233" t="n">
+        <v>8</v>
+      </c>
+      <c r="K233" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2025-04-07 07:02:18</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>0.893478113412318</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>6</v>
+      </c>
+      <c r="G234" t="n">
+        <v>40</v>
+      </c>
+      <c r="H234" t="n">
+        <v>50</v>
+      </c>
+      <c r="I234" t="n">
+        <v>60</v>
+      </c>
+      <c r="J234" t="n">
+        <v>8</v>
+      </c>
+      <c r="K234" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2025-04-07 07:13:40</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>S_RPT</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>0.9955938610073777</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>6</v>
+      </c>
+      <c r="G235" t="n">
+        <v>40</v>
+      </c>
+      <c r="H235" t="n">
+        <v>50</v>
+      </c>
+      <c r="I235" t="n">
+        <v>60</v>
+      </c>
+      <c r="J235" t="n">
+        <v>8</v>
+      </c>
+      <c r="K235" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2025-04-07 07:24:10</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>MTWR</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>0.992663724544266</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>[10, 12]</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>6</v>
+      </c>
+      <c r="G236" t="n">
+        <v>40</v>
+      </c>
+      <c r="H236" t="n">
+        <v>50</v>
+      </c>
+      <c r="I236" t="n">
+        <v>60</v>
+      </c>
+      <c r="J236" t="n">
+        <v>8</v>
+      </c>
+      <c r="K236" t="n">
         <v>9</v>
       </c>
     </row>

--- a/(TESTING) automated_testing/automated_test_log.xlsx
+++ b/(TESTING) automated_testing/automated_test_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NTU document\Academic stuff (NTU)\Y4S1\Final Year Project\Code\JSSP_Env\(TESTING) automated_testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528A0717-53FD-46C4-A255-DC482EF6969B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676E7F5A-54E7-4112-A45F-D4FCA4E3E5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,10 +876,10 @@
     <t>2025-04-08 14:57:26</t>
   </si>
   <si>
+    <t>2025-04-09 11:36:57</t>
+  </si>
+  <si>
     <t>RANDOM</t>
-  </si>
-  <si>
-    <t>2025-04-09 11:36:57</t>
   </si>
   <si>
     <t>2025-04-09 11:41:40</t>
@@ -11380,13 +11380,13 @@
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B293">
         <v>3000</v>
       </c>
       <c r="C293" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D293">
         <v>0.21700193306753651</v>
@@ -11421,7 +11421,7 @@
         <v>3000</v>
       </c>
       <c r="C294" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D294">
         <v>0.579533813095223</v>
@@ -11456,7 +11456,7 @@
         <v>3000</v>
       </c>
       <c r="C295" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D295">
         <v>0.86187738641726375</v>
@@ -11491,7 +11491,7 @@
         <v>3000</v>
       </c>
       <c r="C296" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D296">
         <v>0.96701836879025937</v>
